--- a/DateBase/orders/Nhat 48_2026-7-29.xlsx
+++ b/DateBase/orders/Nhat 48_2026-7-29.xlsx
@@ -1341,6 +1341,9 @@
       <c r="G2" t="str">
         <v>020122218155101212320305105202010555555104512410108415851010193881010355105101010151010510101010101010101051520556112020881510202015105101010510537391120151515</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
